--- a/data/trans_orig/P37A$medicootras-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicootras-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>687080</t>
+          <t>686897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>682675</t>
+          <t>682176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1373719</t>
+          <t>1373435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>963059</t>
+          <t>961414</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1923949</t>
+          <t>1924869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667963</t>
+          <t>668195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>679292</t>
+          <t>677484</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1351523</t>
+          <t>1351524</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1361370</t>
+          <t>1361368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>13445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>934260</t>
+          <t>934306</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1028826</t>
+          <t>1029610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037632</t>
+          <t>1037630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1967216</t>
+          <t>1967389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1977983</t>
+          <t>1977942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3262086</t>
+          <t>3261851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3273636</t>
+          <t>3273564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3364117</t>
+          <t>3364585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3375962</t>
+          <t>3375959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6630818</t>
+          <t>6630316</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6647089</t>
+          <t>6646878</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695924</t>
+          <t>696303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>702741</t>
+          <t>702743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>687866</t>
+          <t>687796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>696038</t>
+          <t>696008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1387230</t>
+          <t>1387470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1397787</t>
+          <t>1397734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>21946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27059</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1004850</t>
+          <t>1005273</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1015843</t>
+          <t>1015816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1011978</t>
+          <t>1010238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1026847</t>
+          <t>1026989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2023072</t>
+          <t>2022697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2040665</t>
+          <t>2040559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>744949</t>
+          <t>744444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>767932</t>
+          <t>767032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776171</t>
+          <t>776174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1519564</t>
+          <t>1518428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1531802</t>
+          <t>1531795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>933602</t>
+          <t>934759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>946669</t>
+          <t>946681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1035323</t>
+          <t>1036377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1048213</t>
+          <t>1048872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1977542</t>
+          <t>1975210</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1993818</t>
+          <t>1992793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>27767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>17138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>59397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3398616</t>
+          <t>3399012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3417513</t>
+          <t>3417003</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3518473</t>
+          <t>3519927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3541306</t>
+          <t>3541171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6926393</t>
+          <t>6925691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6954771</t>
+          <t>6953817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>670400</t>
+          <t>670647</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663258</t>
+          <t>664042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671159</t>
+          <t>671143</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1337288</t>
+          <t>1336494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1345911</t>
+          <t>1345901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20086</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1010295</t>
+          <t>1008511</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1021232</t>
+          <t>1021234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1030045</t>
+          <t>1029249</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1040129</t>
+          <t>1040061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2045258</t>
+          <t>2045413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2059325</t>
+          <t>2059275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>746719</t>
+          <t>746902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757365</t>
+          <t>757391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>775881</t>
+          <t>775313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1527285</t>
+          <t>1527277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1540419</t>
+          <t>1540380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>920853</t>
+          <t>921060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>933677</t>
+          <t>934526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1026895</t>
+          <t>1027002</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1039867</t>
+          <t>1040541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1953390</t>
+          <t>1953257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1971461</t>
+          <t>1971268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>34650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58271</t>
+          <t>58698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3362245</t>
+          <t>3362515</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3381967</t>
+          <t>3381745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3510041</t>
+          <t>3509892</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3530642</t>
+          <t>3530016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6880621</t>
+          <t>6880194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6908336</t>
+          <t>6907063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>631101</t>
+          <t>685076</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>624815</t>
+          <t>677893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>634163</t>
+          <t>688561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>719285</t>
+          <t>727334</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>714067</t>
+          <t>721969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>722364</t>
+          <t>730858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1350387</t>
+          <t>1412409</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1343356</t>
+          <t>1404563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1354934</t>
+          <t>1417539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>26646</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>25190</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1186350</t>
+          <t>1041763</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1173963</t>
+          <t>1029533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1191479</t>
+          <t>1046577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>943610</t>
+          <t>1053438</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>936149</t>
+          <t>1044828</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>948820</t>
+          <t>1060168</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2129961</t>
+          <t>2095201</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2118375</t>
+          <t>2082556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2139298</t>
+          <t>2103401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>17927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>15075</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>701325</t>
+          <t>799274</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>696553</t>
+          <t>794077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>703793</t>
+          <t>802126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>923129</t>
+          <t>800982</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>916283</t>
+          <t>794332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>929582</t>
+          <t>805916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1624453</t>
+          <t>1600257</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1616002</t>
+          <t>1593391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1630887</t>
+          <t>1606671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,67 +7598,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7836</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22130</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12476</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7037</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20941</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18983</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29125</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -7711,69 +7711,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>920324</t>
+          <t>983605</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914546</t>
+          <t>978103</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923646</t>
+          <t>986944</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1105920</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1096911</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1111205</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,02%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1082456</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1073991</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1087895</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2543</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2002780</t>
+          <t>2089526</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1992638</t>
+          <t>2079769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2009641</t>
+          <t>2096123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32778</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>72324</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49790</t>
+          <t>57944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80917</t>
+          <t>89819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3439101</t>
+          <t>3509719</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3427039</t>
+          <t>3497577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3447390</t>
+          <t>3518335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3668480</t>
+          <t>3687673</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3655827</t>
+          <t>3673505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3680173</t>
+          <t>3698825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7107581</t>
+          <t>7197392</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7091180</t>
+          <t>7179897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7122307</t>
+          <t>7211772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
